--- a/Rankings.xlsx
+++ b/Rankings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaeltinetti/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BA730D-EA8B-8F4A-BD27-B1EFBB0306B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F83271-0E7F-CB47-A9E4-77D2C355047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16280" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="170">
   <si>
     <t>Rank</t>
   </si>
@@ -465,13 +465,94 @@
   </si>
   <si>
     <t>Running Point</t>
+  </si>
+  <si>
+    <t>Euphoria</t>
+  </si>
+  <si>
+    <t>Interview with the Vampire</t>
+  </si>
+  <si>
+    <t>Reboot</t>
+  </si>
+  <si>
+    <t>Blue Eye Samurai</t>
+  </si>
+  <si>
+    <t>Warrior</t>
+  </si>
+  <si>
+    <t>The Other Two</t>
+  </si>
+  <si>
+    <t>Daisy Jones and The 6</t>
+  </si>
+  <si>
+    <t>Dark Winds</t>
+  </si>
+  <si>
+    <t>Only Murders In The Building</t>
+  </si>
+  <si>
+    <t>Slow Hosres</t>
+  </si>
+  <si>
+    <t>Colin From Accounts</t>
+  </si>
+  <si>
+    <t>The Day of the Jackal</t>
+  </si>
+  <si>
+    <t>Nobody Wants This</t>
+  </si>
+  <si>
+    <t>Hacks</t>
+  </si>
+  <si>
+    <t>La Maquina</t>
+  </si>
+  <si>
+    <t>Clipped</t>
+  </si>
+  <si>
+    <t>Adolescence</t>
+  </si>
+  <si>
+    <t>Big Boys</t>
+  </si>
+  <si>
+    <t>The Chair Company</t>
+  </si>
+  <si>
+    <t>Dexter: Resurrection</t>
+  </si>
+  <si>
+    <t>Dept. Q</t>
+  </si>
+  <si>
+    <t>The White Lotus</t>
+  </si>
+  <si>
+    <t>Long Story Short</t>
+  </si>
+  <si>
+    <t>Rogue Heroes</t>
+  </si>
+  <si>
+    <t>I Love LA</t>
+  </si>
+  <si>
+    <t>Dying For Sex</t>
+  </si>
+  <si>
+    <t>A Thousand Blows</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -526,6 +607,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -562,7 +650,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -582,6 +670,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -821,7 +910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -831,8 +920,11 @@
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D2" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -841,6 +933,9 @@
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -853,8 +948,11 @@
       <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D4" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -864,8 +962,11 @@
       <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D5" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -875,8 +976,11 @@
       <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D6" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -886,8 +990,11 @@
       <c r="C7" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D7" s="13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -897,8 +1004,11 @@
       <c r="C8" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D8" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -908,24 +1018,33 @@
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D9" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D10" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D11" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -933,6 +1052,9 @@
         <v>16</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>13</v>
       </c>
     </row>
@@ -946,8 +1068,11 @@
       <c r="C13" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D13" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -957,16 +1082,22 @@
       <c r="C14" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D14" s="13" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D15" s="13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -976,8 +1107,11 @@
       <c r="C16" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D16" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -987,8 +1121,11 @@
       <c r="C17" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D17" s="13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -998,174 +1135,209 @@
       <c r="C18" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D18" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D19" s="13" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D20" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D21" s="13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D23" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D24" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D25" s="13"/>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D26" s="13"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D27" s="13"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D28" s="13"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D29" s="13"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D30" s="13"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D31" s="13"/>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D32" s="13"/>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D33" s="13"/>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D34" s="13"/>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D35" s="13"/>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D36" s="13"/>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D37" s="13"/>
+    </row>
+    <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D38" s="13"/>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" ht="13" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" ht="13" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1287,6 +1459,9 @@
       <c r="C2" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="D2" s="13" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="13" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
@@ -1298,6 +1473,9 @@
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="D3" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="G3" s="1"/>
     </row>
@@ -1311,6 +1489,9 @@
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="D4" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" ht="13" x14ac:dyDescent="0.15">
@@ -1323,6 +1504,9 @@
       <c r="C5" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="D5" s="13" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
@@ -1334,6 +1518,9 @@
       <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="D6" s="13" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
@@ -1345,6 +1532,9 @@
       <c r="C7" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="D7" s="13" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="13" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
@@ -1356,6 +1546,9 @@
       <c r="C8" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="D8" s="13" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="13" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
@@ -1367,6 +1560,9 @@
       <c r="C9" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="D9" s="13" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
@@ -1378,6 +1574,9 @@
       <c r="C10" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="D10" s="13" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
@@ -1389,6 +1588,9 @@
       <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="D11" s="13" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="13" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
@@ -1400,16 +1602,22 @@
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="D12" s="13" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="13" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>34</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13" x14ac:dyDescent="0.15">
@@ -1417,10 +1625,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>16</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13" x14ac:dyDescent="0.15">
@@ -1428,9 +1639,12 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>42</v>
       </c>
       <c r="F15" s="4"/>
@@ -1440,10 +1654,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>44</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="13" x14ac:dyDescent="0.15">
@@ -1451,10 +1668,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>46</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>16</v>
       </c>
       <c r="E17" s="2"/>
     </row>
@@ -1463,10 +1683,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>38</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="13" x14ac:dyDescent="0.15">
@@ -1474,10 +1697,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>43</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="E19" s="2"/>
     </row>
@@ -1486,10 +1712,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>50</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>149</v>
       </c>
       <c r="E20" s="2"/>
     </row>
@@ -1498,10 +1727,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>41</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="13" x14ac:dyDescent="0.15">
@@ -1509,10 +1741,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>52</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="13" x14ac:dyDescent="0.15">
@@ -1520,10 +1755,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>48</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="13" x14ac:dyDescent="0.15">
@@ -1531,10 +1769,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>22</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="13" x14ac:dyDescent="0.15">
@@ -1542,10 +1783,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>56</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="13" x14ac:dyDescent="0.15">
@@ -1553,10 +1797,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>58</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="13" x14ac:dyDescent="0.15">
@@ -1564,10 +1811,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>59</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="13" x14ac:dyDescent="0.15">
@@ -1575,9 +1825,12 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="13" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1586,7 +1839,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>53</v>
@@ -1597,7 +1850,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>57</v>
@@ -1606,6 +1859,9 @@
     <row r="31" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>31</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>63</v>
@@ -1684,6 +1940,9 @@
       <c r="D2" s="2" t="s">
         <v>66</v>
       </c>
+      <c r="E2" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
       <c r="K2" s="2"/>
@@ -1699,6 +1958,9 @@
       <c r="D3" s="2" t="s">
         <v>67</v>
       </c>
+      <c r="E3" s="13" t="s">
+        <v>75</v>
+      </c>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
       <c r="K3" s="2"/>
@@ -1716,7 +1978,9 @@
       <c r="D4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="13" t="s">
+        <v>72</v>
+      </c>
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1730,6 +1994,9 @@
       <c r="D5" s="2" t="s">
         <v>72</v>
       </c>
+      <c r="E5" s="13" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="11"/>
@@ -1742,6 +2009,9 @@
       <c r="D6" s="2" t="s">
         <v>73</v>
       </c>
+      <c r="E6" s="13" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="11"/>
@@ -1754,6 +2024,9 @@
       <c r="D7" s="2" t="s">
         <v>69</v>
       </c>
+      <c r="E7" s="13" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="11"/>
@@ -1766,6 +2039,9 @@
       <c r="D8" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="E8" s="13" t="s">
+        <v>152</v>
+      </c>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1779,6 +2055,9 @@
       <c r="D9" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="E9" s="13" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="11"/>
@@ -1791,6 +2070,9 @@
       <c r="D10" s="2" t="s">
         <v>75</v>
       </c>
+      <c r="E10" s="13" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="11"/>
@@ -1803,6 +2085,9 @@
       <c r="D11" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="E11" s="13" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="11"/>
@@ -1815,6 +2100,9 @@
       <c r="D12" s="2" t="s">
         <v>74</v>
       </c>
+      <c r="E12" s="13" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="11"/>
@@ -1827,6 +2115,9 @@
       <c r="D13" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="E13" s="13" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11"/>
@@ -1839,6 +2130,9 @@
       <c r="D14" s="2" t="s">
         <v>77</v>
       </c>
+      <c r="E14" s="13" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="11"/>
@@ -1851,6 +2145,9 @@
       <c r="D15" s="2" t="s">
         <v>78</v>
       </c>
+      <c r="E15" s="13" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="12"/>
@@ -1863,6 +2160,9 @@
       <c r="D16" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="E16" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="5"/>
@@ -1875,6 +2175,9 @@
       <c r="D17" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="E17" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="I17" s="6"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1888,6 +2191,9 @@
       <c r="D18" s="2" t="s">
         <v>81</v>
       </c>
+      <c r="E18" s="13" t="s">
+        <v>85</v>
+      </c>
       <c r="I18" s="6"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1901,6 +2207,9 @@
       <c r="D19" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="E19" s="13" t="s">
+        <v>121</v>
+      </c>
       <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1914,6 +2223,9 @@
       <c r="D20" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="E20" s="13" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="7" t="s">
@@ -1927,6 +2239,9 @@
       </c>
       <c r="D21" s="2" t="s">
         <v>82</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1940,6 +2255,9 @@
       <c r="D22" s="2" t="s">
         <v>86</v>
       </c>
+      <c r="E22" s="13" t="s">
+        <v>39</v>
+      </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
     </row>
@@ -1954,6 +2272,9 @@
       <c r="D23" s="2" t="s">
         <v>87</v>
       </c>
+      <c r="E23" s="13" t="s">
+        <v>155</v>
+      </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
     </row>
@@ -1968,6 +2289,9 @@
       <c r="D24" s="2" t="s">
         <v>88</v>
       </c>
+      <c r="E24" s="13" t="s">
+        <v>156</v>
+      </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
     </row>
@@ -1982,6 +2306,9 @@
       <c r="D25" s="2" t="s">
         <v>79</v>
       </c>
+      <c r="E25" s="13" t="s">
+        <v>157</v>
+      </c>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
     </row>
@@ -1996,6 +2323,9 @@
       <c r="D26" s="2" t="s">
         <v>89</v>
       </c>
+      <c r="E26" s="13" t="s">
+        <v>82</v>
+      </c>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
     </row>
@@ -2010,6 +2340,9 @@
       <c r="D27" s="2" t="s">
         <v>91</v>
       </c>
+      <c r="E27" s="13" t="s">
+        <v>52</v>
+      </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
     </row>
@@ -2023,6 +2356,9 @@
       </c>
       <c r="D28" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>158</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
@@ -5062,6 +5398,7 @@
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="23.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.83203125" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
   </cols>
@@ -5092,6 +5429,9 @@
       <c r="C2" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="D2" s="13" t="s">
+        <v>101</v>
+      </c>
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5104,6 +5444,9 @@
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="D3" s="13" t="s">
+        <v>5</v>
+      </c>
       <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5116,6 +5459,9 @@
       <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="D4" s="13" t="s">
+        <v>8</v>
+      </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5128,6 +5474,9 @@
       <c r="C5" s="2" t="s">
         <v>103</v>
       </c>
+      <c r="D5" s="13" t="s">
+        <v>103</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="H5" s="2"/>
     </row>
@@ -5141,6 +5490,9 @@
       <c r="C6" s="2" t="s">
         <v>104</v>
       </c>
+      <c r="D6" s="13" t="s">
+        <v>105</v>
+      </c>
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5153,6 +5505,9 @@
       <c r="C7" s="2" t="s">
         <v>105</v>
       </c>
+      <c r="D7" s="13" t="s">
+        <v>159</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="H7" s="2"/>
     </row>
@@ -5166,6 +5521,9 @@
       <c r="C8" s="2" t="s">
         <v>107</v>
       </c>
+      <c r="D8" s="13" t="s">
+        <v>107</v>
+      </c>
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5178,6 +5536,9 @@
       <c r="C9" s="2" t="s">
         <v>108</v>
       </c>
+      <c r="D9" s="13" t="s">
+        <v>160</v>
+      </c>
       <c r="F9" s="1"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5190,6 +5551,9 @@
       <c r="C10" s="2" t="s">
         <v>109</v>
       </c>
+      <c r="D10" s="13" t="s">
+        <v>113</v>
+      </c>
       <c r="F10" s="1"/>
       <c r="H10" s="2"/>
     </row>
@@ -5203,6 +5567,9 @@
       <c r="C11" s="2" t="s">
         <v>110</v>
       </c>
+      <c r="D11" s="13" t="s">
+        <v>161</v>
+      </c>
       <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5215,6 +5582,9 @@
       <c r="C12" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="D12" s="13" t="s">
+        <v>111</v>
+      </c>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5227,6 +5597,9 @@
       <c r="C13" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="D13" s="13" t="s">
+        <v>108</v>
+      </c>
       <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5239,6 +5612,9 @@
       <c r="C14" s="2" t="s">
         <v>113</v>
       </c>
+      <c r="D14" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="I14" s="9"/>
     </row>
@@ -5252,6 +5628,9 @@
       <c r="C15" s="2" t="s">
         <v>111</v>
       </c>
+      <c r="D15" s="13" t="s">
+        <v>109</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="H15" s="2"/>
     </row>
@@ -5265,6 +5644,9 @@
       <c r="C16" s="2" t="s">
         <v>115</v>
       </c>
+      <c r="D16" s="13" t="s">
+        <v>115</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="H16" s="2"/>
     </row>
@@ -5278,6 +5660,9 @@
       <c r="C17" s="2" t="s">
         <v>116</v>
       </c>
+      <c r="D17" s="13" t="s">
+        <v>162</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="H17" s="2"/>
     </row>
@@ -5291,7 +5676,9 @@
       <c r="C18" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="1"/>
+      <c r="D18" s="13" t="s">
+        <v>163</v>
+      </c>
       <c r="F18" s="1"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5304,7 +5691,9 @@
       <c r="C19" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D19" s="1"/>
+      <c r="D19" s="13" t="s">
+        <v>116</v>
+      </c>
       <c r="F19" s="1"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5317,7 +5706,9 @@
       <c r="C20" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D20" s="1"/>
+      <c r="D20" s="13" t="s">
+        <v>36</v>
+      </c>
       <c r="F20" s="1"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5330,6 +5721,9 @@
       <c r="C21" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="D21" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="F21" s="1"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5342,7 +5736,9 @@
       <c r="C22" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="1"/>
+      <c r="D22" s="13" t="s">
+        <v>164</v>
+      </c>
       <c r="F22" s="1"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5355,7 +5751,9 @@
       <c r="C23" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D23" s="1"/>
+      <c r="D23" s="13" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
@@ -5367,6 +5765,9 @@
       <c r="C24" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="D24" s="13" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
@@ -5378,6 +5779,9 @@
       <c r="C25" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="D25" s="13" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
@@ -5389,6 +5793,9 @@
       <c r="C26" s="2" t="s">
         <v>122</v>
       </c>
+      <c r="D26" s="13" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
@@ -5400,6 +5807,9 @@
       <c r="C27" s="2" t="s">
         <v>127</v>
       </c>
+      <c r="D27" s="13" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
@@ -5411,6 +5821,9 @@
       <c r="C28" s="2" t="s">
         <v>129</v>
       </c>
+      <c r="D28" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
@@ -5422,6 +5835,9 @@
       <c r="C29" s="2" t="s">
         <v>131</v>
       </c>
+      <c r="D29" s="13" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
@@ -5433,6 +5849,9 @@
       <c r="C30" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="D30" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
@@ -5444,6 +5863,9 @@
       <c r="C31" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="D31" s="13" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
@@ -5455,8 +5877,11 @@
       <c r="C32" s="2" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D32" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -5466,8 +5891,11 @@
       <c r="C33" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D33" s="13" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -5477,8 +5905,11 @@
       <c r="C34" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D34" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -5488,8 +5919,11 @@
       <c r="C35" s="2" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D35" s="13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -5499,32 +5933,44 @@
       <c r="C36" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D36" s="13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D37" s="13" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D38" s="13" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>38</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D39" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -5532,7 +5978,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -5540,7 +5986,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -5548,32 +5994,32 @@
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>47</v>
       </c>
